--- a/docs/vessel-packaging-workbook.xlsx
+++ b/docs/vessel-packaging-workbook.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="92">
   <si>
     <t xml:space="preserve">VESSEL — Packaging Assumptions (editable inputs)</t>
   </si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Total Per-Order Components Required (before waste) — cloths/cards/stickers/boxes</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirmed supplier-payment facts (for the packaging value/deposit breakdown)</t>
+    <t xml:space="preserve">Confirmed supplier-payment facts (whole invoice — no line-item allocation)</t>
   </si>
   <si>
     <t xml:space="preserve">Total Supplier Invoice Value (US$)</t>
@@ -153,61 +153,58 @@
     <t xml:space="preserve">CONFIRMED — full supplier order invoice total, 10 Aug 2026.</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Supplier Deposit Already Paid (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONFIRMED — ~50% of the ₪7,000 total committed supplier cost. This deposit was NOT allocated to individual invoice lines.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Supplier Balance Remaining (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONFIRMED — due before shipment, per the whole supplier invoice.</t>
+    <t xml:space="preserve">Total Supplier Deposit Already Paid (₪, approximate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIRMED — ~50% of the ~₪7,000 total committed supplier cost, for the WHOLE invoice. Not allocated to individual invoice lines — no per-line deposit split is a confirmed fact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Supplier Balance Remaining (₪, approximate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIRMED — due before shipment, for the whole supplier invoice.</t>
   </si>
   <si>
     <t xml:space="preserve">VESSEL — Packaging Component Requirements &amp; Costs</t>
   </si>
   <si>
-    <t xml:space="preserve">Required quantities are driven ONLY by the packaging rule x Assumptions — never netted against Quoted Qty. 'Remaining Qty Needed' compares against Ordered Qty (what is actually committed), not Quoted Qty (what a vendor has merely priced). 'Recommended Qty to Order' rounds up to the vendor's MOQ once known; MOQ is left UNKNOWN rather than assumed where no lot size is confirmed anywhere in the source material.</t>
+    <t xml:space="preserve">Vendors quote fixed lots, not a per-unit rate you can buy any quantity of. 'Economic Usage Cost' values what is actually consumed at the quoted rate, for planning only — it is NOT a real purchase option unless the required quantity happens to equal the quoted lot. 'Actual Cash Required' is what you would really pay: ₪0 if already covered by stock on order, the FULL lot price if the only quoted lot is adequate and nothing is on order yet, or UNKNOWN if the only quoted lot is too small and no covering quote exists.</t>
   </si>
   <si>
     <t xml:space="preserve">Component</t>
   </si>
   <si>
-    <t xml:space="preserve">Quoted Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordered Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Received Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculated Qty Required (before waste)</t>
+    <t xml:space="preserve">Required Qty (before waste)</t>
   </si>
   <si>
     <t xml:space="preserve">Required Qty incl. Waste Buffer</t>
   </si>
   <si>
-    <t xml:space="preserve">Quoted Qty Sufficient?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remaining Qty Needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor MOQ / Lot Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommended Qty to Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected Surplus After Ordering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit Cost (₪)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash Required (Actual Order Qty)</t>
+    <t xml:space="preserve">Available Quoted Purchase Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available Quoted Purchase Price (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quoted Unit Rate (₪)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic Usage Cost at Quoted Rate (₪) — analytical only, NOT a purchase price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote Adequate for Required Qty?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already Ordered Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already Received Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Cash Required for Available Purchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surplus After Purchase</t>
   </si>
   <si>
     <t xml:space="preserve">Notes / Source</t>
@@ -216,9 +213,6 @@
     <t xml:space="preserve">Pouches (velvet, logo-embossed)</t>
   </si>
   <si>
-    <t xml:space="preserve">N/A — bundled in jewelry supplier order</t>
-  </si>
-  <si>
     <t xml:space="preserve">Part of the jewelry supplier's invoice (10 Aug 2026); ordered together with the jewelry, ~50% paid, in production. Not yet received — confirm and inspect on arrival.</t>
   </si>
   <si>
@@ -228,40 +222,34 @@
     <t xml:space="preserve">Thank-You Cards</t>
   </si>
   <si>
-    <t xml:space="preserve">UNKNOWN - confirm with vendor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUOTED ONLY: ₪250 for 1,000 (₪0.25 each). Not ordered, not paid, not received.</t>
+    <t xml:space="preserve">Only quoted lot on record: 1,000 for ₪250. Not ordered, not paid, not received. You cannot buy just the ~110 needed at this rate — the full 1,000-card lot is the only known purchase option.</t>
   </si>
   <si>
     <t xml:space="preserve">Stickers</t>
   </si>
   <si>
-    <t xml:space="preserve">QUOTED ONLY: ₪80 for 100 (₪0.80 each). Not ordered, not paid, not received. This row is the sticker-sufficiency check.</t>
+    <t xml:space="preserve">Only quoted lot on record: 100 for ₪80 — INSUFFICIENT for the required quantity. No quote exists yet for a lot that actually covers what's needed. This row is the sticker-sufficiency check.</t>
   </si>
   <si>
     <t xml:space="preserve">Cardboard Shipping Boxes (unprinted)</t>
   </si>
   <si>
-    <t xml:space="preserve">QUOTED ONLY: ₪700 for 160 unprinted (₪4.375 each). Not ordered, not paid, not received. Printing cost is a separate line below.</t>
+    <t xml:space="preserve">Only quoted lot on record: 160 unprinted for ₪700. Not ordered, not paid, not received. Printing cost is a separate line below. The full 160-box lot is the only known purchase option.</t>
   </si>
   <si>
     <t xml:space="preserve">Box Printing (add-on, per box)</t>
   </si>
   <si>
-    <t xml:space="preserve">N/A - tied to box order, no separate lot size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printing cost has not been quoted. Quantity mirrors the box requirement above; printing is priced per box, not a separately stocked item.</t>
+    <t xml:space="preserve">No fixed-lot quote exists for printing at all yet — cost has not been obtained from any vendor. Quantity mirrors the box requirement above; printing is priced per box, not a separately stocked item.</t>
   </si>
   <si>
     <t xml:space="preserve">VESSEL — Packaging Summary (auto-calculated)</t>
   </si>
   <si>
-    <t xml:space="preserve">Every figure below is a formula reading 'Assumptions' and 'Component Requirements &amp; Costs'. Figures that depend on an unresolved input (box printing, VAT status, vendor delivery) display UNKNOWN or INCOMPLETE - COST UNKNOWN rather than silently computing as if that cost were zero.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full Program Value (all required components at cost, as quoted — excludes printing)</t>
+    <t xml:space="preserve">Every figure below is a formula reading 'Assumptions' and 'Component Requirements &amp; Costs'. 'Cash required' figures reflect real, purchasable vendor lots — never a linear fraction of a bulk quote. Figures that depend on an unresolved input (an inadequate sticker quote, box printing, VAT status, vendor delivery) display UNKNOWN or INCOMPLETE - COST UNKNOWN rather than silently computing as zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Program Economic Value (all required components valued at their quoted unit rate — an analytical value, NOT a purchase price; excludes printing)</t>
   </si>
   <si>
     <t xml:space="preserve">Supplier-order packaging value &amp; deposit status (informational — not additive to cash-required figures below)</t>
@@ -270,25 +258,25 @@
     <t xml:space="preserve">Total Pouch/Cloth Value Included in Supplier Invoice</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Supplier Deposit Already Paid (whole invoice — not allocated by line)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Supplier Balance Remaining (whole invoice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODEL ASSUMPTION (not a fact) — IF the deposit were allocated proportionally by invoice value, packaging's illustrative share of the paid deposit would be:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional cash required (new purchases only — pouches/cloths excluded, see note above)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As quoted (components only, excl. printing/VAT/delivery)</t>
+    <t xml:space="preserve">Total Supplier Deposit Already Paid (approximate, whole invoice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Supplier Balance Remaining (approximate, whole invoice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional cash required (new purchases only — pouches/cloths need none, see note above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known quoted cash required (cards + boxes — full available lots, the only purchasable quantities at a known price)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stickers (only quoted lot is insufficient — see Component sheet)</t>
   </si>
   <si>
     <t xml:space="preserve">Box printing add-on</t>
   </si>
   <si>
-    <t xml:space="preserve">VAT adjustment (applied to the 'as quoted' components subtotal only)</t>
+    <t xml:space="preserve">VAT adjustment (applied to the known quoted cash-required figure only)</t>
   </si>
   <si>
     <t xml:space="preserve">Vendor delivery (flat)</t>
@@ -297,7 +285,7 @@
     <t xml:space="preserve">TOTAL ADDITIONAL CASH REQUIRED (all-in)</t>
   </si>
   <si>
-    <t xml:space="preserve">Packaging cost per order</t>
+    <t xml:space="preserve">Packaging cost per order (economic allocation at quoted unit rate — NOT a claim about purchasable quantities)</t>
   </si>
   <si>
     <t xml:space="preserve">Per normal order (1 item: 1 pouch, 1 cloth, 1 card, 1 sticker, 1 box + printing)</t>
@@ -326,7 +314,7 @@
     <numFmt numFmtId="170" formatCode="\₪#,##0"/>
     <numFmt numFmtId="171" formatCode="\₪#,##0.0000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,13 +398,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -505,7 +486,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -582,26 +563,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -623,14 +600,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -920,7 +889,7 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1199,20 +1168,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1231,7 +1199,6 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -1249,9 +1216,8 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>49</v>
       </c>
@@ -1291,314 +1257,287 @@
       <c r="M4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="20" t="n">
         <f aca="false">Assumptions!B24</f>
         <v>120</v>
       </c>
-      <c r="F5" s="20" t="n">
-        <f aca="false">ROUNDUP(E5*(1+Assumptions!B12),0)</f>
+      <c r="C5" s="19" t="n">
+        <f aca="false">ROUNDUP(B5*(1+Assumptions!B12),0)</f>
         <v>126</v>
       </c>
-      <c r="G5" s="19" t="str">
-        <f aca="false">IF(B5&gt;=F5,"Yes","NO - quote insufficient")</f>
+      <c r="D5" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <f aca="false">D5*Assumptions!B14*Assumptions!B13</f>
+        <v>499.94</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <f aca="false">E5/D5</f>
+        <v>0.99988</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <f aca="false">C5*F5</f>
+        <v>125.98488</v>
+      </c>
+      <c r="H5" s="22" t="str">
+        <f aca="false">IF(D5&gt;=C5,"Yes","NO - insufficient")</f>
         <v>Yes</v>
       </c>
-      <c r="H5" s="20" t="n">
-        <f aca="false">MAX(0,F5-C5)</f>
+      <c r="I5" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="J5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <f aca="false">IF(H5=0,0,IF(ISNUMBER(I5),CEILING(H5,I5),H5))</f>
+      <c r="K5" s="20" t="n">
+        <f aca="false">IF(I5&gt;=C5,0,IF(H5="Yes",E5,"UNKNOWN - no quote covers required quantity"))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="20" t="n">
-        <f aca="false">(C5+J5)-F5</f>
+      <c r="L5" s="19" t="n">
+        <f aca="false">IF(I5&gt;=C5,I5-C5,IF(H5="Yes",(I5+D5)-C5,"UNKNOWN"))</f>
         <v>374</v>
       </c>
-      <c r="L5" s="21" t="n">
-        <f aca="false">Assumptions!B14*Assumptions!B13</f>
-        <v>0.99988</v>
-      </c>
-      <c r="M5" s="22" t="n">
-        <f aca="false">J5*L5</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>65</v>
+      <c r="M5" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="20" t="n">
         <f aca="false">Assumptions!B25</f>
         <v>104.347826086957</v>
       </c>
-      <c r="F6" s="20" t="n">
-        <f aca="false">ROUNDUP(E6*(1+Assumptions!B12),0)</f>
+      <c r="C6" s="19" t="n">
+        <f aca="false">ROUNDUP(B6*(1+Assumptions!B12),0)</f>
         <v>110</v>
       </c>
-      <c r="G6" s="19" t="str">
-        <f aca="false">IF(B6&gt;=F6,"Yes","NO - quote insufficient")</f>
+      <c r="D6" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <f aca="false">D6*Assumptions!B15*Assumptions!B13</f>
+        <v>357.1</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <f aca="false">E6/D6</f>
+        <v>0.7142</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <f aca="false">C6*F6</f>
+        <v>78.562</v>
+      </c>
+      <c r="H6" s="22" t="str">
+        <f aca="false">IF(D6&gt;=C6,"Yes","NO - insufficient")</f>
         <v>Yes</v>
       </c>
-      <c r="H6" s="20" t="n">
-        <f aca="false">MAX(0,F6-C6)</f>
+      <c r="I6" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="J6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <f aca="false">IF(H6=0,0,IF(ISNUMBER(I6),CEILING(H6,I6),H6))</f>
+      <c r="K6" s="20" t="n">
+        <f aca="false">IF(I6&gt;=C6,0,IF(H6="Yes",E6,"UNKNOWN - no quote covers required quantity"))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="20" t="n">
-        <f aca="false">(C6+J6)-F6</f>
+      <c r="L6" s="19" t="n">
+        <f aca="false">IF(I6&gt;=C6,I6-C6,IF(H6="Yes",(I6+D6)-C6,"UNKNOWN"))</f>
         <v>390</v>
       </c>
-      <c r="L6" s="21" t="n">
-        <f aca="false">Assumptions!B15*Assumptions!B13</f>
-        <v>0.7142</v>
-      </c>
-      <c r="M6" s="22" t="n">
-        <f aca="false">J6*L6</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="s">
+      <c r="M6" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="B7" s="19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="20" t="n">
         <f aca="false">Assumptions!B25</f>
         <v>104.347826086957</v>
       </c>
-      <c r="F7" s="20" t="n">
-        <f aca="false">ROUNDUP(E7*(1+Assumptions!B12),0)</f>
+      <c r="C7" s="19" t="n">
+        <f aca="false">ROUNDUP(B7*(1+Assumptions!B12),0)</f>
         <v>110</v>
       </c>
-      <c r="G7" s="19" t="str">
-        <f aca="false">IF(B7&gt;=F7,"Yes","NO - quote insufficient")</f>
+      <c r="D7" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <f aca="false">E7/D7</f>
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <f aca="false">C7*F7</f>
+        <v>27.5</v>
+      </c>
+      <c r="H7" s="22" t="str">
+        <f aca="false">IF(D7&gt;=C7,"Yes","NO - insufficient")</f>
         <v>Yes</v>
       </c>
-      <c r="H7" s="20" t="n">
-        <f aca="false">MAX(0,F7-C7)</f>
-        <v>110</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="20" t="n">
-        <f aca="false">IF(H7=0,0,IF(ISNUMBER(I7),CEILING(H7,I7),H7))</f>
-        <v>110</v>
+      <c r="I7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="K7" s="20" t="n">
-        <f aca="false">(C7+J7)-F7</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M7" s="22" t="n">
-        <f aca="false">J7*L7</f>
-        <v>27.5</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(I7&gt;=C7,0,IF(H7="Yes",E7,"UNKNOWN - no quote covers required quantity"))</f>
+        <v>250</v>
+      </c>
+      <c r="L7" s="19" t="n">
+        <f aca="false">IF(I7&gt;=C7,I7-C7,IF(H7="Yes",(I7+D7)-C7,"UNKNOWN"))</f>
+        <v>890</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B8" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="20" t="n">
         <f aca="false">Assumptions!B25</f>
         <v>104.347826086957</v>
       </c>
-      <c r="F8" s="20" t="n">
-        <f aca="false">ROUNDUP(E8*(1+Assumptions!B12),0)</f>
+      <c r="C8" s="19" t="n">
+        <f aca="false">ROUNDUP(B8*(1+Assumptions!B12),0)</f>
         <v>110</v>
       </c>
-      <c r="G8" s="19" t="str">
-        <f aca="false">IF(B8&gt;=F8,"Yes","NO - quote insufficient")</f>
-        <v>NO - quote insufficient</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <f aca="false">MAX(0,F8-C8)</f>
-        <v>110</v>
-      </c>
-      <c r="I8" s="23" t="s">
+      <c r="D8" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <f aca="false">E8/D8</f>
+        <v>0.8</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <f aca="false">C8*F8</f>
+        <v>88</v>
+      </c>
+      <c r="H8" s="22" t="str">
+        <f aca="false">IF(D8&gt;=C8,"Yes","NO - insufficient")</f>
+        <v>NO - insufficient</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="20" t="str">
+        <f aca="false">IF(I8&gt;=C8,0,IF(H8="Yes",E8,"UNKNOWN - no quote covers required quantity"))</f>
+        <v>UNKNOWN - no quote covers required quantity</v>
+      </c>
+      <c r="L8" s="19" t="str">
+        <f aca="false">IF(I8&gt;=C8,I8-C8,IF(H8="Yes",(I8+D8)-C8,"UNKNOWN"))</f>
+        <v>UNKNOWN</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <f aca="false">IF(H8=0,0,IF(ISNUMBER(I8),CEILING(H8,I8),H8))</f>
-        <v>110</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <f aca="false">(C8+J8)-F8</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <f aca="false">J8*L8</f>
-        <v>88</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B9" s="19" t="n">
-        <v>160</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="20" t="n">
         <f aca="false">Assumptions!B25</f>
         <v>104.347826086957</v>
       </c>
-      <c r="F9" s="20" t="n">
-        <f aca="false">ROUNDUP(E9*(1+Assumptions!B12),0)</f>
+      <c r="C9" s="19" t="n">
+        <f aca="false">ROUNDUP(B9*(1+Assumptions!B12),0)</f>
         <v>110</v>
       </c>
-      <c r="G9" s="19" t="str">
-        <f aca="false">IF(B9&gt;=F9,"Yes","NO - quote insufficient")</f>
+      <c r="D9" s="19" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>700</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <f aca="false">E9/D9</f>
+        <v>4.375</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <f aca="false">C9*F9</f>
+        <v>481.25</v>
+      </c>
+      <c r="H9" s="22" t="str">
+        <f aca="false">IF(D9&gt;=C9,"Yes","NO - insufficient")</f>
         <v>Yes</v>
       </c>
-      <c r="H9" s="20" t="n">
-        <f aca="false">MAX(0,F9-C9)</f>
-        <v>110</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <f aca="false">IF(H9=0,0,IF(ISNUMBER(I9),CEILING(H9,I9),H9))</f>
-        <v>110</v>
+      <c r="I9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="K9" s="20" t="n">
-        <f aca="false">(C9+J9)-F9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="21" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <f aca="false">J9*L9</f>
-        <v>481.25</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>73</v>
+        <f aca="false">IF(I9&gt;=C9,0,IF(H9="Yes",E9,"UNKNOWN - no quote covers required quantity"))</f>
+        <v>700</v>
+      </c>
+      <c r="L9" s="19" t="n">
+        <f aca="false">IF(I9&gt;=C9,I9-C9,IF(H9="Yes",(I9+D9)-C9,"UNKNOWN"))</f>
+        <v>50</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="20" t="n">
-        <f aca="false">E9</f>
+        <v>71</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <f aca="false">B9</f>
         <v>104.347826086957</v>
       </c>
-      <c r="F10" s="20" t="n">
-        <f aca="false">F9</f>
+      <c r="C10" s="19" t="n">
+        <f aca="false">C9</f>
         <v>110</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20" t="n">
-        <f aca="false">F10</f>
-        <v>110</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <f aca="false">IF(H10=0,0,IF(ISNUMBER(I10),CEILING(H10,I10),H10))</f>
-        <v>110</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <f aca="false">(0+J10)-F10</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="21" t="str">
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="21" t="str">
         <f aca="false">IF(ISBLANK(Assumptions!B19),"UNKNOWN",Assumptions!B19)</f>
         <v>UNKNOWN</v>
       </c>
-      <c r="M10" s="19" t="str">
-        <f aca="false">IF(ISNUMBER(L10),J10*L10,"UNKNOWN")</f>
+      <c r="G10" s="20" t="str">
+        <f aca="false">IF(ISNUMBER(F10),C10*F10,"UNKNOWN")</f>
         <v>UNKNOWN</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>76</v>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="20" t="str">
+        <f aca="false">IF(ISNUMBER(F10),C10*F10,"UNKNOWN")</f>
+        <v>UNKNOWN</v>
+      </c>
+      <c r="L10" s="22"/>
+      <c r="M10" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1620,13 +1559,13 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1637,204 +1576,204 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25" t="n">
+        <f aca="false">SUM('Component Requirements &amp; Costs'!G5:G9)</f>
+        <v>801.29688</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="25" t="n">
+        <f aca="false">'Component Requirements &amp; Costs'!E5+'Component Requirements &amp; Costs'!E6</f>
+        <v>857.04</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26" t="n">
-        <f aca="false">SUMPRODUCT('Component Requirements &amp; Costs'!F5:F9,'Component Requirements &amp; Costs'!L5:L9)</f>
-        <v>801.29688</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="26" t="n">
-        <f aca="false">'Component Requirements &amp; Costs'!C5*Assumptions!B14*Assumptions!B13+'Component Requirements &amp; Costs'!C6*Assumptions!B15*Assumptions!B13</f>
-        <v>857.04</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29" t="n">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="n">
         <f aca="false">Assumptions!B29</f>
         <v>3500</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29" t="n">
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28" t="n">
         <f aca="false">Assumptions!B30</f>
         <v>3500</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
+    <row r="11" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="25" t="n">
+        <f aca="false">'Component Requirements &amp; Costs'!K7+'Component Requirements &amp; Costs'!K9</f>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="25" t="str">
+        <f aca="false">'Component Requirements &amp; Costs'!K8</f>
+        <v>UNKNOWN - no quote covers required quantity</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="25" t="str">
+        <f aca="false">'Component Requirements &amp; Costs'!K10</f>
+        <v>UNKNOWN</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31" t="n">
-        <f aca="false">(('Component Requirements &amp; Costs'!C5*Assumptions!B14+'Component Requirements &amp; Costs'!C6*Assumptions!B15)/Assumptions!B28)*Assumptions!B29</f>
-        <v>428.549563797765</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="25" t="str">
+        <f aca="false">IF(Assumptions!B16="Yes",0,IF(Assumptions!B16="No",F12*Assumptions!B17,"UNKNOWN"))</f>
+        <v>UNKNOWN</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="26" t="n">
-        <f aca="false">SUM('Component Requirements &amp; Costs'!M5:M9)</f>
-        <v>596.75</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="26" t="str">
-        <f aca="false">'Component Requirements &amp; Costs'!M10</f>
-        <v>UNKNOWN</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="26" t="str">
-        <f aca="false">IF(Assumptions!B16="Yes",0,IF(Assumptions!B16="No",F13*Assumptions!B17,"UNKNOWN"))</f>
-        <v>UNKNOWN</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="26" t="str">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="25" t="str">
         <f aca="false">IF(ISBLANK(Assumptions!B18),"UNKNOWN",Assumptions!B18)</f>
         <v>UNKNOWN</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="29" t="str">
+        <f aca="false">IF(AND(ISNUMBER(F13),ISNUMBER(F14),ISNUMBER(F15),ISNUMBER(F16)),F12+F13+F14+F15+F16,"INCOMPLETE - COST UNKNOWN")</f>
+        <v>INCOMPLETE - COST UNKNOWN</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="30" t="str">
+        <f aca="false">IF(ISNUMBER('Component Requirements &amp; Costs'!F10),'Component Requirements &amp; Costs'!F5+'Component Requirements &amp; Costs'!F6+'Component Requirements &amp; Costs'!F7+'Component Requirements &amp; Costs'!F8+'Component Requirements &amp; Costs'!F9+'Component Requirements &amp; Costs'!F10,"INCOMPLETE - COST UNKNOWN (printing not yet quoted)")</f>
+        <v>INCOMPLETE - COST UNKNOWN (printing not yet quoted)</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="30" t="str">
+        <f aca="false">IF(ISNUMBER('Component Requirements &amp; Costs'!F10),'Component Requirements &amp; Costs'!F5*2+'Component Requirements &amp; Costs'!F6+'Component Requirements &amp; Costs'!F7+'Component Requirements &amp; Costs'!F8+'Component Requirements &amp; Costs'!F9+'Component Requirements &amp; Costs'!F10,"INCOMPLETE - COST UNKNOWN (printing not yet quoted)")</f>
+        <v>INCOMPLETE - COST UNKNOWN (printing not yet quoted)</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="32" t="str">
-        <f aca="false">IF(AND(ISNUMBER(F14),ISNUMBER(F15),ISNUMBER(F16)),F13+F14+F15+F16,"INCOMPLETE - COST UNKNOWN")</f>
-        <v>INCOMPLETE - COST UNKNOWN</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="27" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="33" t="str">
-        <f aca="false">IF(ISNUMBER('Component Requirements &amp; Costs'!L10),'Component Requirements &amp; Costs'!L5+'Component Requirements &amp; Costs'!L6+'Component Requirements &amp; Costs'!L7+'Component Requirements &amp; Costs'!L8+'Component Requirements &amp; Costs'!L9+'Component Requirements &amp; Costs'!L10,"INCOMPLETE - COST UNKNOWN (printing not yet quoted)")</f>
-        <v>INCOMPLETE - COST UNKNOWN (printing not yet quoted)</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="33" t="str">
-        <f aca="false">IF(ISNUMBER('Component Requirements &amp; Costs'!L10),'Component Requirements &amp; Costs'!L5*2+'Component Requirements &amp; Costs'!L6+'Component Requirements &amp; Costs'!L7+'Component Requirements &amp; Costs'!L8+'Component Requirements &amp; Costs'!L9+'Component Requirements &amp; Costs'!L10,"INCOMPLETE - COST UNKNOWN (printing not yet quoted)")</f>
-        <v>INCOMPLETE - COST UNKNOWN (printing not yet quoted)</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="34" t="str">
-        <f aca="false">IF('Component Requirements &amp; Costs'!B8&gt;='Component Requirements &amp; Costs'!F8,"Sufficient - quote covers requirement","SHORTFALL - quoted 100 is NOT enough, and 0 are currently ordered")</f>
-        <v>SHORTFALL - quoted 100 is NOT enough, and 0 are currently ordered</v>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="31" t="str">
+        <f aca="false">IF('Component Requirements &amp; Costs'!D8&gt;='Component Requirements &amp; Costs'!C8,"Sufficient - quote covers requirement","SHORTFALL - quoted 100 is NOT enough, 0 are currently ordered, and the price for an adequate quantity is unknown")</f>
+        <v>SHORTFALL - quoted 100 is NOT enough, 0 are currently ordered, and the price for an adequate quantity is unknown</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1784,7 @@
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
